--- a/docs/files/2026-09-24/상담행정공고_2026-09-24.xlsx
+++ b/docs/files/2026-09-24/상담행정공고_2026-09-24.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="공고" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="공고" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$11</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'공고'!$A$1:$O$12</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'공고'!$1:$1</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -431,7 +431,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O11"/>
+  <dimension ref="A1:O12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1034,28 +1034,28 @@
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>상담</t>
+          <t>상담 · 복지</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr"/>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>이음</t>
+          <t>양천해누리복지관</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>임상심리치료전문인력 채용</t>
+          <t>[양천해누리복지관] 심리운동사 채용공고(건강누리팀)</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>계약직</t>
+          <t>정규직</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>경기도 시흥시</t>
+          <t>서울특별시 양천구</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr"/>
@@ -1066,17 +1066,17 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-10-16</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>D-5</t>
+          <t>D-22</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr"/>
@@ -1088,7 +1088,7 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1066336</t>
         </is>
       </c>
     </row>
@@ -1101,12 +1101,12 @@
       <c r="B10" s="2" t="inlineStr"/>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
+          <t>이음</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
+          <t>임상심리치료전문인력 채용</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
@@ -1116,28 +1116,28 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>경기도 수원시</t>
+          <t>경기도 시흥시</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr"/>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-15</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-09-29</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>D-7</t>
+          <t>D-5</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr"/>
@@ -1149,25 +1149,25 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1067909</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>상담 · 청소년 · 복지 · 교육</t>
+          <t>상담</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr"/>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관</t>
+          <t>굿네이버스 경원본부 아주좋은이웃심리치유센터</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+          <t>굿네이버스 경기지부 아주좋은이웃심리치유센터 놀이치료사 모집</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1177,28 +1177,28 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>경기도</t>
+          <t>경기도 수원시</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr"/>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2026-09-18</t>
+          <t>2026-09-16</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-01</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>D-11</t>
+          <t>D-7</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr"/>
@@ -1210,12 +1210,73 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
+          <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068302</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>상담 · 청소년 · 복지 · 교육</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr"/>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>용인시처인장애인복지관 장애아동발달재활사업 미술심리재활강사 모집 공고</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>계약직</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>경기도</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>2026-10-05</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>D-11</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr"/>
+      <c r="M12" s="2" t="inlineStr"/>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>복지넷</t>
+        </is>
+      </c>
+      <c r="O12" s="2" t="inlineStr">
+        <is>
           <t>https://www.bokji.net/job/off/01_01.bokji?ID=1068718</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O11"/>
+  <autoFilter ref="A1:O12"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
